--- a/RESULTS/tables/survival_cox_ml_risk_score.xlsx
+++ b/RESULTS/tables/survival_cox_ml_risk_score.xlsx
@@ -482,13 +482,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.6744827751316</v>
+        <v>1.667077056015118</v>
       </c>
       <c r="D2" t="n">
-        <v>1.657734449155416</v>
+        <v>1.651288332677126</v>
       </c>
       <c r="E2" t="n">
-        <v>1.691400311817706</v>
+        <v>1.68301674256148</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -512,13 +512,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.647275819556712</v>
+        <v>1.640865292990839</v>
       </c>
       <c r="D3" t="n">
-        <v>1.618686464984898</v>
+        <v>1.613601375755976</v>
       </c>
       <c r="E3" t="n">
-        <v>1.676370121326464</v>
+        <v>1.668589869961222</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
